--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -820,13 +820,13 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
   </si>
   <si>
-    <t xml:space="preserve">Résultat de l'évaluation - Le type et la valeur du résultat de l'évaluation (value) dépendent du volet utilisant cette entrée (les précisions sont alors fournies dans le volet correspondant). </t>
+    <t>Résultat de l'évaluation - Le type et la valeur du résultat de l'évaluation (value) dépendent du volet utilisant cette entrée (les précisions sont alors fournies dans le volet correspondant).</t>
   </si>
   <si>
     <t>Résultat de l'évaluation</t>
@@ -896,9 +896,6 @@
   </si>
   <si>
     <t>Observation.interpretationCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Interprétation </t>
   </si>
   <si>
     <t>Interprétation</t>
@@ -10078,7 +10075,7 @@
         <v>287</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10109,7 +10106,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -10147,10 +10144,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10206,7 +10203,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10224,7 +10221,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10244,10 +10241,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10274,7 +10271,7 @@
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10325,7 +10322,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10345,10 +10342,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10371,7 +10368,7 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10424,7 +10421,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10444,10 +10441,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10470,7 +10467,7 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10523,7 +10520,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10543,10 +10540,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10569,7 +10566,7 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10622,7 +10619,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -10642,10 +10639,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10668,7 +10665,7 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10721,7 +10718,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10741,10 +10738,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10767,7 +10764,7 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10820,7 +10817,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10840,10 +10837,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10866,7 +10863,7 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10919,7 +10916,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -10939,10 +10936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10965,7 +10962,7 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11018,7 +11015,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11038,10 +11035,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11139,10 +11136,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11240,10 +11237,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11341,10 +11338,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11442,10 +11439,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11545,10 +11542,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11648,10 +11645,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11751,10 +11748,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11854,10 +11851,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11884,7 +11881,7 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11955,10 +11952,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11995,7 +11992,7 @@
         <v>75</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>75</v>
@@ -12014,25 +12011,25 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12052,10 +12049,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12082,7 +12079,7 @@
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12094,46 +12091,46 @@
         <v>75</v>
       </c>
       <c r="S104" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12153,10 +12150,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12183,12 +12180,12 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
@@ -12234,7 +12231,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12254,10 +12251,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12333,7 +12330,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12353,10 +12350,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12379,7 +12376,7 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12432,7 +12429,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -12452,10 +12449,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12478,7 +12475,7 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12531,7 +12528,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12551,10 +12548,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12577,7 +12574,7 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12630,7 +12627,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -12650,10 +12647,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12676,7 +12673,7 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12729,7 +12726,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -12749,10 +12746,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12775,7 +12772,7 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12828,7 +12825,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -12848,10 +12845,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12874,7 +12871,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12927,7 +12924,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -12947,10 +12944,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12973,7 +12970,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13026,7 +13023,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13046,10 +13043,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13072,7 +13069,7 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13125,7 +13122,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13145,10 +13142,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13171,7 +13168,7 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13224,7 +13221,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13244,10 +13241,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13270,7 +13267,7 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13323,7 +13320,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -13343,10 +13340,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13369,7 +13366,7 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13422,7 +13419,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13442,10 +13439,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13468,7 +13465,7 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13521,7 +13518,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -13541,10 +13538,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13567,7 +13564,7 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13620,7 +13617,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -13640,10 +13637,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13666,7 +13663,7 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13719,7 +13716,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -13739,10 +13736,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13765,11 +13762,11 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13820,7 +13817,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -13840,10 +13837,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13941,10 +13938,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14042,10 +14039,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14143,10 +14140,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14244,10 +14241,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14347,10 +14344,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14450,10 +14447,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14553,10 +14550,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14656,10 +14653,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14686,7 +14683,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14757,10 +14754,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14794,7 +14791,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>75</v>
@@ -14816,7 +14813,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>75</v>
@@ -14834,7 +14831,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -14854,10 +14851,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14880,7 +14877,7 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14933,7 +14930,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -14953,10 +14950,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14979,7 +14976,7 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15032,7 +15029,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
